--- a/tools/명단_양식.xlsx
+++ b/tools/명단_양식.xlsx
@@ -1,65 +1,159 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4da3161df6971ecc/Desktop/kyk2-ticket/kyk2-ticket/tools/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_0BBB0F6E8CAA05F3A6CE37060611FCE1F64E6830" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22ACD82C-66E9-4C9B-B67D-3BD68F364E5E}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명단" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성안내" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="명단" sheetId="1" r:id="rId1"/>
+    <sheet name="작성안내" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>연락처</t>
+  </si>
+  <si>
+    <t>구역</t>
+  </si>
+  <si>
+    <t>좌석</t>
+  </si>
+  <si>
+    <t>등급</t>
+  </si>
+  <si>
+    <t>홍길동</t>
+  </si>
+  <si>
+    <t>010-1234-5678</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>3열 / 4번</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>3열 / 5번</t>
+  </si>
+  <si>
+    <t>김민지</t>
+  </si>
+  <si>
+    <t>010-9876-4321</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>7열 / 12번</t>
+  </si>
+  <si>
+    <t>[작성 방법]</t>
+  </si>
+  <si>
+    <t>· '명단' 시트의 2~4행은 예시입니다. 지우고 실제 명단을 입력하세요. (제목 행은 유지)</t>
+  </si>
+  <si>
+    <t>· 같은 사람에게 좌석이 여러 개면 행을 여러 줄로 나눠 입력하세요. (예시의 홍길동 참고)</t>
+  </si>
+  <si>
+    <t>· 연락처는 전체 번호 입력. 조회에는 뒤 4자리만 쓰이고 티켓에는 표시되지 않습니다.</t>
+  </si>
+  <si>
+    <t>· 구역/좌석은 입력한 그대로 티켓에 표시됩니다. ('구역','좌석' 단어는 자동으로 붙습니다)</t>
+  </si>
+  <si>
+    <t>· 등급 열은 선택 사항이며, 입력 시 티켓 상단에 작은 배지로 표시됩니다.</t>
+  </si>
+  <si>
+    <t>· 작성 후 admin.html 페이지에 이 파일을 올리면 db.json이 생성됩니다.</t>
+  </si>
+  <si>
+    <t>조성윤</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7B7795"/>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007B7795"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFE97132"/>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00E97132"/>
-      <sz val="10"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF4C4870"/>
       <name val="맑은 고딕"/>
-      <color rgb="004C4870"/>
-      <sz val="10"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B1760"/>
+        <fgColor rgb="FF1B1760"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,105 +167,47 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C9C6E0"/>
+        <color rgb="FFC9C6E0"/>
       </left>
       <right style="thin">
-        <color rgb="00C9C6E0"/>
+        <color rgb="FFC9C6E0"/>
       </right>
       <top style="thin">
-        <color rgb="00C9C6E0"/>
+        <color rgb="FFC9C6E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C9C6E0"/>
+        <color rgb="FFC9C6E0"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -459,192 +495,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>구역</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>좌석</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>등급</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>010-1234-5678</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>3열 / 4번</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>010-1234-5678</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>3열 / 5번</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>김민지</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>010-9876-4321</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7열 / 12번</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1080300948</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>[작성 방법]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>· '명단' 시트의 2~4행은 예시입니다. 지우고 실제 명단을 입력하세요. (제목 행은 유지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>· 같은 사람에게 좌석이 여러 개면 행을 여러 줄로 나눠 입력하세요. (예시의 홍길동 참고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>· 연락처는 전체 번호 입력. 조회에는 뒤 4자리만 쓰이고 티켓에는 표시되지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>· 구역/좌석은 입력한 그대로 티켓에 표시됩니다. ('구역','좌석' 단어는 자동으로 붙습니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>· 등급 열은 선택 사항이며, 입력 시 티켓 상단에 작은 배지로 표시됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>· 작성 후 admin.html 페이지에 이 파일을 올리면 db.json이 생성됩니다.</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/명단_양식.xlsx
+++ b/tools/명단_양식.xlsx
@@ -1,163 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4da3161df6971ecc/Desktop/kyk2-ticket/kyk2-ticket/tools/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0BBB0F6E8CAA05F3A6CE37060611FCE1F64E6830" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22ACD82C-66E9-4C9B-B67D-3BD68F364E5E}"/>
-  <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="명단" sheetId="1" r:id="rId1"/>
-    <sheet name="작성안내" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
-  <si>
-    <t>이름</t>
-  </si>
-  <si>
-    <t>연락처</t>
-  </si>
-  <si>
-    <t>구역</t>
-  </si>
-  <si>
-    <t>좌석</t>
-  </si>
-  <si>
-    <t>등급</t>
-  </si>
-  <si>
-    <t>홍길동</t>
-  </si>
-  <si>
-    <t>010-1234-5678</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>3열 / 4번</t>
-  </si>
-  <si>
-    <t>VIP</t>
-  </si>
-  <si>
-    <t>3열 / 5번</t>
-  </si>
-  <si>
-    <t>김민지</t>
-  </si>
-  <si>
-    <t>010-9876-4321</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>7열 / 12번</t>
-  </si>
-  <si>
-    <t>[작성 방법]</t>
-  </si>
-  <si>
-    <t>· '명단' 시트의 2~4행은 예시입니다. 지우고 실제 명단을 입력하세요. (제목 행은 유지)</t>
-  </si>
-  <si>
-    <t>· 같은 사람에게 좌석이 여러 개면 행을 여러 줄로 나눠 입력하세요. (예시의 홍길동 참고)</t>
-  </si>
-  <si>
-    <t>· 연락처는 전체 번호 입력. 조회에는 뒤 4자리만 쓰이고 티켓에는 표시되지 않습니다.</t>
-  </si>
-  <si>
-    <t>· 구역/좌석은 입력한 그대로 티켓에 표시됩니다. ('구역','좌석' 단어는 자동으로 붙습니다)</t>
-  </si>
-  <si>
-    <t>· 등급 열은 선택 사항이며, 입력 시 티켓 상단에 작은 배지로 표시됩니다.</t>
-  </si>
-  <si>
-    <t>· 작성 후 admin.html 페이지에 이 파일을 올리면 db.json이 생성됩니다.</t>
-  </si>
-  <si>
-    <t>조성윤</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7B7795"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFE97132"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF4C4870"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B1760"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -165,49 +60,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9C6E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFC9C6E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9C6E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC9C6E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -286,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -320,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -354,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -489,140 +351,145 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="B1" t="str">
+        <v>소분류</v>
+      </c>
+      <c r="C1" t="str">
+        <v>연락처</v>
+      </c>
+      <c r="D1" t="str">
+        <v>구역</v>
+      </c>
+      <c r="E1" t="str">
+        <v>좌석</v>
+      </c>
+      <c r="F1" t="str">
+        <v>등급</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1080300948</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>정지인</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>010-1234-5678</v>
+      </c>
+      <c r="D2" t="str">
+        <v>203구역</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2열 3번</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>정지인</v>
+      </c>
+      <c r="B3" t="str">
+        <v>권기환</v>
+      </c>
+      <c r="C3" t="str">
+        <v>010-1234-5678</v>
+      </c>
+      <c r="D3" t="str">
+        <v>203구역</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2열 4번</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2"/>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>김철수</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>010-9876-4321</v>
+      </c>
+      <c r="D4" t="str">
+        <v>216구역</v>
+      </c>
+      <c r="E4" t="str">
+        <v>7열 5번</v>
+      </c>
+      <c r="F4" t="str">
+        <v>VIP</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="90" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/명단_양식.xlsx
+++ b/tools/명단_양식.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="명단" sheetId="1" r:id="rId1"/>
+    <sheet name="안내" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,14 +398,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +429,16 @@
       <c r="F1" t="str">
         <v>등급</v>
       </c>
+      <c r="G1" t="str">
+        <v>비표대상</v>
+      </c>
+      <c r="H1" t="str">
+        <v>인원</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>정지인</v>
+        <v>홍길동</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -438,58 +447,120 @@
         <v>010-1234-5678</v>
       </c>
       <c r="D2" t="str">
-        <v>203구역</v>
+        <v>R1구역</v>
       </c>
       <c r="E2" t="str">
-        <v>2열 3번</v>
+        <v>1번</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>VIP</v>
+      </c>
+      <c r="G2" t="str">
+        <v>O</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>정지인</v>
+        <v>홍길동</v>
       </c>
       <c r="B3" t="str">
-        <v>권기환</v>
+        <v>김동행</v>
       </c>
       <c r="C3" t="str">
         <v>010-1234-5678</v>
       </c>
       <c r="D3" t="str">
-        <v>203구역</v>
+        <v>R1구역</v>
       </c>
       <c r="E3" t="str">
-        <v>2열 4번</v>
+        <v>2번</v>
       </c>
       <c r="F3" t="str">
+        <v>VIP</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>김철수</v>
+        <v>김민수</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>010-9876-4321</v>
+        <v>010-2222-3333</v>
       </c>
       <c r="D4" t="str">
-        <v>216구역</v>
+        <v>I1구역</v>
       </c>
       <c r="E4" t="str">
-        <v>7열 5번</v>
+        <v>12번</v>
       </c>
       <c r="F4" t="str">
-        <v>VIP</v>
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <cols>
+    <col min="1" max="1" width="92.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>안내</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>· 조회는 대분류 + 연락처 뒤 4자리 · 같은 사람 좌석 여러 매 = 행 여러 줄(대분류·연락처 동일)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>· 소분류: 동반인 이름(선택) — 티켓에 "대분류 (소분류)"로 표기</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>· 비표대상: O 표시 = 비표 수령 대상 (한 행에만 표시해도 그 사람 전체에 적용, 빈칸 = 일반)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>· 인원: 비표 매수(선택, 빈칸이면 1) · 등급: VIP 표기 등 선택</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>· 대상자는 티켓 확인 시 "씨유 앞 인포데스크에서 비표 수령 → VIP입구 입장" 팝업이 뜹니다</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/명단_양식.xlsx
+++ b/tools/명단_양식.xlsx
@@ -540,22 +540,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>· 소분류: 동반인 이름(선택) — 티켓에 "대분류 (소분류)"로 표기</v>
+        <v>· 소분류: 동반인 이름(선택) — 티켓에 "대분류 (소분류)" 표기 · 등급: VIP 표기 등(선택)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>· 비표대상: O 표시 = 비표 수령 대상 (한 행에만 표시해도 그 사람 전체에 적용, 빈칸 = 일반)</v>
+        <v>· 비표대상: O 표시 = 비표 수령 대상(빈칸 = 일반) — 한 행에만 표시해도 그 사람 전체 적용</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>· 인원: 비표 매수(선택, 빈칸이면 1) · 등급: VIP 표기 등 선택</v>
+        <v>· 인원: 비표 매수(선택, 빈칸이면 1)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>· 대상자는 티켓 확인 시 "씨유 앞 인포데스크에서 비표 수령 → VIP입구 입장" 팝업이 뜹니다</v>
+        <v>· 비표 대상자는 티켓 확인 시 "씨유 앞 인포데스크에서 비표 수령 → VIP입구 입장" 팝업이 뜹니다</v>
       </c>
     </row>
   </sheetData>

--- a/tools/명단_양식.xlsx
+++ b/tools/명단_양식.xlsx
@@ -398,16 +398,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I5"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
     <col min="7" max="7" width="9.83203125" customWidth="1"/>
     <col min="8" max="8" width="6.83203125" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,6 +436,9 @@
       <c r="H1" t="str">
         <v>인원</v>
       </c>
+      <c r="I1" t="str">
+        <v>지류티켓</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -461,6 +465,9 @@
       <c r="H2">
         <v>2</v>
       </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -487,6 +494,9 @@
       <c r="H3" t="str">
         <v/>
       </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -513,17 +523,49 @@
       <c r="H4" t="str">
         <v/>
       </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>박종이</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>010-7777-8888</v>
+      </c>
+      <c r="D5" t="str">
+        <v>A2구역</v>
+      </c>
+      <c r="E5" t="str">
+        <v>1열 1~4번</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>O</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <cols>
     <col min="1" max="1" width="92.83203125" customWidth="1"/>
   </cols>
@@ -535,32 +577,27 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>· 조회는 대분류 + 연락처 뒤 4자리 · 같은 사람 좌석 여러 매 = 행 여러 줄(대분류·연락처 동일)</v>
+        <v>· 조회는 이름(대분류 또는 방문자명) + 연락처 뒤 4자리 · 좌석은 "1열 1~10번"처럼 범위·쉼표로 적으면 한 장씩 분리</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>· 소분류: 동반인 이름(선택) — 티켓에 "대분류 (소분류)" 표기 · 등급: VIP 표기 등(선택)</v>
+        <v>· 비표대상 O = 티켓 확인 시 "인포데스크 비표 수령 → VIP입구" 팝업 (인원 = 비표 매수)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>· 비표대상: O 표시 = 비표 수령 대상(빈칸 = 일반) — 한 행에만 표시해도 그 사람 전체 적용</v>
+        <v>· 지류티켓 O = QR·입장확인 없이 구역·좌석이 크게 적힌 화면 + "인포데스크에서 종이 티켓 교환" 안내</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>· 인원: 비표 매수(선택, 빈칸이면 1)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>· 비표 대상자는 티켓 확인 시 "씨유 앞 인포데스크에서 비표 수령 → VIP입구 입장" 팝업이 뜹니다</v>
+        <v>· 대분류가 비어 있으면 소분류를 이름으로 사용</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/명단_양식.xlsx
+++ b/tools/명단_양식.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -408,7 +408,6 @@
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
     <col min="7" max="7" width="9.83203125" customWidth="1"/>
     <col min="8" max="8" width="6.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,9 +435,6 @@
       <c r="H1" t="str">
         <v>인원</v>
       </c>
-      <c r="I1" t="str">
-        <v>지류티켓</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -465,9 +461,6 @@
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -494,9 +487,6 @@
       <c r="H3" t="str">
         <v/>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -523,49 +513,17 @@
       <c r="H4" t="str">
         <v/>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>박종이</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>010-7777-8888</v>
-      </c>
-      <c r="D5" t="str">
-        <v>A2구역</v>
-      </c>
-      <c r="E5" t="str">
-        <v>1열 1~4번</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>O</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <cols>
     <col min="1" max="1" width="92.83203125" customWidth="1"/>
   </cols>
@@ -587,17 +545,12 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>· 지류티켓 O = QR·입장확인 없이 구역·좌석이 크게 적힌 화면 + "인포데스크에서 종이 티켓 교환" 안내</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
         <v>· 대분류가 비어 있으면 소분류를 이름으로 사용</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A4"/>
   </ignoredErrors>
 </worksheet>
 </file>